--- a/raw_data/P4_1990_2009/P4_raw_metadata_final.xlsx
+++ b/raw_data/P4_1990_2009/P4_raw_metadata_final.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf938313c90dc4d1/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F79C6299-F39B-4C50-9B8C-5E39B8920DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C12C0DDE-08DC-42C4-9C54-EBE35FE04176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A48B0D59-4E40-4F4E-9E8F-4725E160BD96}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7109A6C5-539B-46AB-8A59-8C902477E99B}"/>
   </bookViews>
   <sheets>
-    <sheet name="P4_raw_metadata_final" sheetId="1" r:id="rId1"/>
+    <sheet name="P4_raw_metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="187">
   <si>
     <t>file_id</t>
   </si>
@@ -94,6 +94,39 @@
     <t>P4_2009_091</t>
   </si>
   <si>
+    <t>ما_بعد_جدیدیت_مضمرات_و_ممکنات_وہاب_اشرفی</t>
+  </si>
+  <si>
+    <t>ندیم_کی_غزلوں_کا_تجزیاتی_مطالعہڈاکٹر_ناہید_قاسمی</t>
+  </si>
+  <si>
+    <t>Ar_Raheeq_Al_Makhtum</t>
+  </si>
+  <si>
+    <t>Biography</t>
+  </si>
+  <si>
+    <t>Manto_Nama</t>
+  </si>
+  <si>
+    <t>Rajinder_Singh_Bedi_Shakhsiyat_Aur_Fan</t>
+  </si>
+  <si>
+    <t>Sach_Mohabbat_Aur_Zara_Sa_Keena</t>
+  </si>
+  <si>
+    <t>Shibli_Ki_Hayat_e_Maashqa</t>
+  </si>
+  <si>
+    <t>میرے_ماہ_و_سال_یاداشیں_مصنف_جاوید_شاہین_2003ء_ناشر_فکشن_ہاؤس_لاہور</t>
+  </si>
+  <si>
+    <t>ملکہ_وکٹوریہ_اور_منشی_عبدالکریم</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
     <t>P4_1999_071</t>
   </si>
   <si>
@@ -344,6 +377,210 @@
   </si>
   <si>
     <t>P4_2009_044</t>
+  </si>
+  <si>
+    <t>مارکس_اور_مشرق_سبط_حسن</t>
+  </si>
+  <si>
+    <t>Politics</t>
+  </si>
+  <si>
+    <t>میرا_پاکستانی_سفر_نامہ_بلراج_ساہنی_مترجم_یاسر_جواد</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>P4_2002_092</t>
+  </si>
+  <si>
+    <t>P4_2002_093</t>
+  </si>
+  <si>
+    <t>P4_2002_094</t>
+  </si>
+  <si>
+    <t>P4_2002_095</t>
+  </si>
+  <si>
+    <t>P4_2002_096</t>
+  </si>
+  <si>
+    <t>P4_2002_128</t>
+  </si>
+  <si>
+    <t>P4_2002_129</t>
+  </si>
+  <si>
+    <t>P4_2002_130</t>
+  </si>
+  <si>
+    <t>P4_2002_144</t>
+  </si>
+  <si>
+    <t>P4_2002_145</t>
+  </si>
+  <si>
+    <t>P4_2002_146</t>
+  </si>
+  <si>
+    <t>P4_2002_147</t>
+  </si>
+  <si>
+    <t>P4_2002_148</t>
+  </si>
+  <si>
+    <t>P4_2002_149</t>
+  </si>
+  <si>
+    <t>P4_2002_150</t>
+  </si>
+  <si>
+    <t>P4_2002_151</t>
+  </si>
+  <si>
+    <t>P4_2002_152</t>
+  </si>
+  <si>
+    <t>P4_2002_153</t>
+  </si>
+  <si>
+    <t>P4_2002_154</t>
+  </si>
+  <si>
+    <t>P4_2002_155</t>
+  </si>
+  <si>
+    <t>P4_2003_106</t>
+  </si>
+  <si>
+    <t>P4_2003_107</t>
+  </si>
+  <si>
+    <t>P4_2003_108</t>
+  </si>
+  <si>
+    <t>P4_2003_109</t>
+  </si>
+  <si>
+    <t>P4_2003_110</t>
+  </si>
+  <si>
+    <t>P4_2003_111</t>
+  </si>
+  <si>
+    <t>P4_2003_112</t>
+  </si>
+  <si>
+    <t>P4_2003_113</t>
+  </si>
+  <si>
+    <t>P4_2003_114</t>
+  </si>
+  <si>
+    <t>P4_2003_115</t>
+  </si>
+  <si>
+    <t>P4_1999_138</t>
+  </si>
+  <si>
+    <t>P4_1999_139</t>
+  </si>
+  <si>
+    <t>P4_1999_140</t>
+  </si>
+  <si>
+    <t>P4_1999_141</t>
+  </si>
+  <si>
+    <t>P4_1999_142</t>
+  </si>
+  <si>
+    <t>P4_1999_143</t>
+  </si>
+  <si>
+    <t>P4_2003_120</t>
+  </si>
+  <si>
+    <t>P4_2003_121</t>
+  </si>
+  <si>
+    <t>P4_2003_122</t>
+  </si>
+  <si>
+    <t>P4_2003_123</t>
+  </si>
+  <si>
+    <t>P4_2003_124</t>
+  </si>
+  <si>
+    <t>P4_2003_125</t>
+  </si>
+  <si>
+    <t>P4_2003_126</t>
+  </si>
+  <si>
+    <t>P4_2003_127</t>
+  </si>
+  <si>
+    <t>P4_2005_133</t>
+  </si>
+  <si>
+    <t>P4_2005_134</t>
+  </si>
+  <si>
+    <t>P4_2005_135</t>
+  </si>
+  <si>
+    <t>P4_2005_136</t>
+  </si>
+  <si>
+    <t>P4_2005_137</t>
+  </si>
+  <si>
+    <t>P4_2003_100</t>
+  </si>
+  <si>
+    <t>P4_2003_101</t>
+  </si>
+  <si>
+    <t>P4_2003_102</t>
+  </si>
+  <si>
+    <t>P4_2003_103</t>
+  </si>
+  <si>
+    <t>P4_2003_104</t>
+  </si>
+  <si>
+    <t>P4_2003_105</t>
+  </si>
+  <si>
+    <t>P4_2004_131</t>
+  </si>
+  <si>
+    <t>P4_2004_132</t>
+  </si>
+  <si>
+    <t>P4_2009_116</t>
+  </si>
+  <si>
+    <t>P4_2009_117</t>
+  </si>
+  <si>
+    <t>P4_2009_118</t>
+  </si>
+  <si>
+    <t>P4_2009_119</t>
+  </si>
+  <si>
+    <t>P4_1997_097</t>
+  </si>
+  <si>
+    <t>P4_1997_098</t>
+  </si>
+  <si>
+    <t>P4_1997_099</t>
   </si>
 </sst>
 </file>
@@ -1206,15 +1443,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8C7327-EF18-4D88-92F1-26901CD0C4B9}">
-  <dimension ref="A1:E87"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF25EEE-6920-4ACB-B3C1-1F79A957DD05}">
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="1"/>
-    <col min="4" max="4" width="10.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1491,1209 +1728,2297 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C17" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1">
-        <v>1551</v>
+        <v>8075</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1">
-        <v>1891</v>
+        <v>28693</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1">
-        <v>1752</v>
+        <v>25575</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E20" s="1">
-        <v>1447</v>
+        <v>27861</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E21" s="1">
-        <v>3991</v>
+        <v>20467</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E22" s="1">
-        <v>2135</v>
+        <v>22558</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1">
-        <v>1689</v>
+        <v>21950</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E24" s="1">
-        <v>1774</v>
+        <v>17944</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1">
-        <v>2301</v>
+        <v>18246</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1">
-        <v>2629</v>
+        <v>21314</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1">
-        <v>1583</v>
+        <v>22132</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1">
-        <v>1050</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C29" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1">
-        <v>3417</v>
+        <v>23109</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1">
-        <v>1991</v>
+        <v>2002</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1">
-        <v>3761</v>
+        <v>22195</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C31" s="1">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E31" s="1">
-        <v>2834</v>
+        <v>32852</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E32" s="1">
-        <v>1579</v>
+        <v>27173</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C33" s="1">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E33" s="1">
-        <v>2588</v>
+        <v>17702</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C34" s="1">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1">
-        <v>4155</v>
+        <v>29784</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1">
-        <v>9747</v>
+        <v>16470</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C36" s="1">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1">
-        <v>4683</v>
+        <v>26299</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C37" s="1">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1">
-        <v>3876</v>
+        <v>19671</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C38" s="1">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E38" s="1">
-        <v>4087</v>
+        <v>17504</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C39" s="1">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1">
-        <v>3767</v>
+        <v>16932</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C40" s="1">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1">
-        <v>5247</v>
+        <v>16597</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C41" s="1">
-        <v>1990</v>
+        <v>2003</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E41" s="1">
-        <v>1011</v>
+        <v>22077</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C42" s="1">
-        <v>1990</v>
+        <v>2003</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E42" s="1">
-        <v>1097</v>
+        <v>29013</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C43" s="1">
-        <v>1991</v>
+        <v>2003</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E43" s="1">
-        <v>909</v>
+        <v>10654</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C44" s="1">
-        <v>1991</v>
+        <v>2003</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E44" s="1">
-        <v>479</v>
+        <v>21904</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C45" s="1">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E45" s="1">
-        <v>1242</v>
+        <v>24380</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C46" s="1">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E46" s="1">
-        <v>1139</v>
+        <v>17259</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C47" s="1">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E47" s="1">
-        <v>450</v>
+        <v>34514</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C48" s="1">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E48" s="1">
-        <v>395</v>
+        <v>22168</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C49" s="1">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E49" s="1">
-        <v>534</v>
+        <v>13822</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C50" s="1">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E50" s="1">
-        <v>667</v>
+        <v>24641</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C51" s="1">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E51" s="1">
-        <v>832</v>
+        <v>25621</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C52" s="1">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E52" s="1">
-        <v>389</v>
+        <v>31863</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C53" s="1">
-        <v>1996</v>
+        <v>2003</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E53" s="1">
-        <v>1683</v>
+        <v>25660</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C54" s="1">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E54" s="1">
-        <v>512</v>
+        <v>17099</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C55" s="1">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E55" s="1">
-        <v>967</v>
+        <v>31444</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C56" s="1">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E56" s="1">
-        <v>397</v>
+        <v>18729</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C57" s="1">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E57" s="1">
-        <v>461</v>
+        <v>17947</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C58" s="1">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E58" s="1">
-        <v>705</v>
+        <v>23788</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C59" s="1">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E59" s="1">
-        <v>667</v>
+        <v>31087</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C60" s="1">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E60" s="1">
-        <v>660</v>
+        <v>31791</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C61" s="1">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1">
-        <v>227</v>
+        <v>21024</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C62" s="1">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1">
-        <v>148</v>
+        <v>20572</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C63" s="1">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E63" s="1">
-        <v>914</v>
+        <v>32552</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C64" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E64" s="1">
-        <v>188</v>
+        <v>26428</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C65" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E65" s="1">
-        <v>625</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E66" s="1">
-        <v>194</v>
+        <v>9183</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C67" s="1">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E67" s="1">
-        <v>748</v>
+        <v>9453</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C68" s="1">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E68" s="1">
-        <v>263</v>
+        <v>11718</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C69" s="1">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E69" s="1">
-        <v>295</v>
+        <v>15017</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C70" s="1">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E70" s="1">
-        <v>1170</v>
+        <v>26555</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E71" s="1">
-        <v>94</v>
+        <v>9712</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="C72" s="1">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="E72" s="1">
-        <v>648</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="E73" s="1">
-        <v>491</v>
+        <v>27945</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C74" s="1">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E74" s="1">
-        <v>439</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C75" s="1">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E75" s="1">
-        <v>149</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C76" s="1">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E76" s="1">
-        <v>1576</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C77" s="1">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E77" s="1">
-        <v>252</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C78" s="1">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E78" s="1">
-        <v>261</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C79" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E79" s="1">
-        <v>152</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C80" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E80" s="1">
-        <v>735</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E81" s="1">
-        <v>684</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E82" s="1">
-        <v>871</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C83" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E83" s="1">
-        <v>1129</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E84" s="1">
-        <v>1401</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C85" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E85" s="1">
-        <v>1145</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C86" s="1">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E86" s="1">
-        <v>1248</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1991</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E87" s="1">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E88" s="1">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C89" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E90" s="1">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E92" s="1">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E93" s="1">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" s="1">
+        <v>3876</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E95" s="1">
+        <v>4087</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1999</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E96" s="1">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1999</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E97" s="1">
+        <v>5247</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1990</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1990</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1991</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E100" s="1">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1991</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E101" s="1">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E104" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C105" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E105" s="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1994</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E106" s="1">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1994</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E107" s="1">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1995</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E108" s="1">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1995</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" s="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1996</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E111" s="1">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E112" s="1">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E113" s="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1999</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E114" s="1">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C115" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E115" s="1">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C116" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E116" s="1">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C117" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E117" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C118" s="1">
+        <v>2003</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E118" s="1">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C119" s="1">
+        <v>2003</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E119" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C120" s="1">
+        <v>2003</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E120" s="1">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C121" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E121" s="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C122" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E122" s="1">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C123" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E123" s="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C124" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E124" s="1">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C125" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E125" s="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C126" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E126" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C127" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C128" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E128" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C129" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E129" s="1">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C130" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E130" s="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C131" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E131" s="1">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C132" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E132" s="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C133" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E133" s="1">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C87" s="1">
+      <c r="B134" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C134" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E134" s="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C135" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E135" s="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C136" s="1">
         <v>2009</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E87" s="1">
+      <c r="D136" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E136" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C137" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E137" s="1">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C138" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E138" s="1">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C139" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E139" s="1">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C140" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E140" s="1">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C141" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E141" s="1">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C142" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E142" s="1">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C143" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E143" s="1">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C144" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E144" s="1">
         <v>1079</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C145" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E145" s="1">
+        <v>13485</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C146" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E146" s="1">
+        <v>21005</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C147" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E147" s="1">
+        <v>16790</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C148" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E148" s="1">
+        <v>13724</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E149" s="1">
+        <v>17886</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E150" s="1">
+        <v>9162</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E151" s="1">
+        <v>31403</v>
       </c>
     </row>
   </sheetData>
